--- a/lab/ornek/kalibre-lab-sample-result.xlsx
+++ b/lab/ornek/kalibre-lab-sample-result.xlsx
@@ -116,7 +116,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7d0ff99169fdf3b630e57e74e8d86c316ca0e757633ff2e39437e960d0b5473f</t>
+          <t xml:space="preserve">e62670676d24e858eab5255262522c360379175a3a524a247cee505ca1feff81</t>
         </is>
       </c>
     </row>

--- a/lab/ornek/kalibre-lab-sample-result.xlsx
+++ b/lab/ornek/kalibre-lab-sample-result.xlsx
@@ -80,7 +80,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYNTHETIC SAMPLE. The prices are generated, the dates (2030) are fictional. Educational sample, not investment advice.</t>
+          <t xml:space="preserve">Example.</t>
         </is>
       </c>
     </row>
@@ -116,7 +116,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">e62670676d24e858eab5255262522c360379175a3a524a247cee505ca1feff81</t>
+          <t xml:space="preserve">798f677e801391c9ecb1550562e7823cdf4520bf68c0189af774777f0fbfdeab</t>
         </is>
       </c>
     </row>
